--- a/src/main/resources/testData/TestData.xlsx
+++ b/src/main/resources/testData/TestData.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khanb\eclipse-workspace\EcommerceWeb3March\src\main\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080CDEF9-ACFF-440A-AB66-C46766D71E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38C58C8-0637-4115-97F6-673D8D0DA382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B4C53ABB-F5C3-4E04-AEEA-4BA68035D0D7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{B4C53ABB-F5C3-4E04-AEEA-4BA68035D0D7}"/>
   </bookViews>
   <sheets>
     <sheet name="SignupData" sheetId="1" r:id="rId1"/>
+    <sheet name="ValidLoginData" sheetId="2" r:id="rId2"/>
+    <sheet name="InvalidLoginData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Kamran</t>
   </si>
@@ -138,13 +140,22 @@
   </si>
   <si>
     <t>Sara</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>wrong@test.com</t>
+  </si>
+  <si>
+    <t>kamran44@mailinator.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +167,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -178,10 +197,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,8 +209,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -684,4 +717,106 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25447E02-9879-416E-878B-CE7E9132F43B}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.7265625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{F4582D2F-87EE-4BA3-B514-59CDA1602770}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{C7B075A6-C389-487E-98C1-A9BC02B3BC67}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BF53B2-96F3-4C1A-91BD-47E400CBC9F3}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.7265625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="mailto:wrong@test.com" xr:uid="{CE9447A7-7431-4144-9695-ECEC5E5F1387}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/testData/TestData.xlsx
+++ b/src/main/resources/testData/TestData.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khanb\eclipse-workspace\EcommerceWeb3March\src\main\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38C58C8-0637-4115-97F6-673D8D0DA382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F9DC1B-7FA4-49E5-B535-06BC8BBD62FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{B4C53ABB-F5C3-4E04-AEEA-4BA68035D0D7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{B4C53ABB-F5C3-4E04-AEEA-4BA68035D0D7}"/>
   </bookViews>
   <sheets>
     <sheet name="SignupData" sheetId="1" r:id="rId1"/>
     <sheet name="ValidLoginData" sheetId="2" r:id="rId2"/>
     <sheet name="InvalidLoginData" sheetId="3" r:id="rId3"/>
+    <sheet name="CategoryData" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>Kamran</t>
   </si>
@@ -149,6 +150,24 @@
   </si>
   <si>
     <t>kamran44@mailinator.com</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>subCategory</t>
+  </si>
+  <si>
+    <t>Women</t>
+  </si>
+  <si>
+    <t>Dress</t>
+  </si>
+  <si>
+    <t>Tops</t>
+  </si>
+  <si>
+    <t>Saree</t>
   </si>
 </sst>
 </file>
@@ -201,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,10 +234,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -721,53 +737,90 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25447E02-9879-416E-878B-CE7E9132F43B}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.7265625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.26953125" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
-      <c r="B6" s="6"/>
+      <c r="B6" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{F4582D2F-87EE-4BA3-B514-59CDA1602770}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{C7B075A6-C389-487E-98C1-A9BC02B3BC67}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{2F255090-8B21-4BDE-BAE6-41949021C918}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{D40A67D1-2707-4CAA-B334-66794AAFE48E}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{A63E6823-A181-4697-ADA7-66B63ED7129A}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{915F700F-D8FD-44B9-975B-23EC68F73404}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -811,7 +864,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
-      <c r="B6" s="6"/>
+      <c r="B6" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -819,4 +872,17 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B71E5B-01A9-4B7C-B1EA-9EEEF25B06E4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/testData/TestData.xlsx
+++ b/src/main/resources/testData/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khanb\eclipse-workspace\EcommerceWeb3March\src\main\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F9DC1B-7FA4-49E5-B535-06BC8BBD62FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A45FA45-FB52-4B88-8F73-D18CA1FC9A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{B4C53ABB-F5C3-4E04-AEEA-4BA68035D0D7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
   <si>
     <t>Kamran</t>
   </si>
@@ -168,6 +168,18 @@
   </si>
   <si>
     <t>Saree</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>Polo</t>
+  </si>
+  <si>
+    <t>H&amp;M</t>
+  </si>
+  <si>
+    <t>Biba</t>
   </si>
 </sst>
 </file>
@@ -737,7 +749,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25447E02-9879-416E-878B-CE7E9132F43B}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.7265625" customWidth="1"/>
@@ -746,7 +758,7 @@
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>34</v>
       </c>
@@ -759,8 +771,11 @@
       <c r="D1" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -773,8 +788,11 @@
       <c r="D2" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -787,8 +805,11 @@
       <c r="D3" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>36</v>
       </c>
@@ -801,12 +822,15 @@
       <c r="D4" s="5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
     </row>
